--- a/technology_surveys/050_teacher_technology_survey--technology_surveys.xlsx
+++ b/technology_surveys/050_teacher_technology_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,35 +520,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>teacher_experience_with_technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teacher Information</t>
+          <t>What is your experience level with technology in the classroom?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>technology_used_for_communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technical Skills</t>
+          <t>What technology platforms do you use for communication with students and parents?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,40 +561,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>hours_spent_on_professional_development</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technology Used</t>
+          <t>How many hours do you spend per week on professional development using technology?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>technical_skills_needed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Equipment Needed</t>
+          <t>What type of technical skills do you think are essential for teachers to have?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>technical_training</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Knowledge and Skills</t>
+          <t>Have you received any technical training or certifications in the past 2 years?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>top_technologies_used</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>What are the top 3 technologies that you use in your classroom?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,23 +653,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>technical_support</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Technical Training</t>
+          <t>How many hours of technical support do you receive from your school's IT department per week?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>lacking_skills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technology Used in Class</t>
+          <t>What are the top 3 technical skills that teachers in your school lack?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,69 +699,69 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>technical_issues</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology Skills Required</t>
+          <t>Have you had any issues with technology in the past year?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>technical_support_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Equipment Needed</t>
+          <t>How many hours do you spend on technical issues per week?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_11</t>
+          <t>future_technology_usage</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>What would you like to see in the future regarding technology usage in school?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_12</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Teacher Information</t>
+          <t>Any additional comments?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_13</t>
+          <t>technical_skills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Technical Skills and Knowledge</t>
+          <t>What technical skills do you need to improve your teaching practice?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,131 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_14</t>
+          <t>technical_skills_and_knowledge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology Used</t>
+          <t>What technical skills and knowledge would you like to acquire?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Technical Training</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Technology Used in Class</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Skills and Knowledge</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Technical Skills and Knowledge</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Technical Skills and Knowledge</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,109 +873,109 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>technology_used_for_communication_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>technology_used_for_communication_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>online_forum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Online forum</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>technology_used_for_communication_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>technical_skills_needed_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Programming</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>technical_skills_needed_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Data analysis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>technical_skills_needed_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>multimedia_design</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Multimedia design</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>technical_training_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1107,7 +992,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>technical_training_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1124,272 +1009,204 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>top_technologies_used_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>top_technologies_used_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>top_technologies_used_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>lacking_skills_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Programming</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>lacking_skills_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Data analysis</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>lacking_skills_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>multimedia_design</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Multimedia design</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>technical_skills_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>presentation_design</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Presentation design</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>technical_skills_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Data analysis</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>page_16_choices</t>
+          <t>technical_skills_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online_resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Online resources</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>page_16_choices</t>
+          <t>technical_skills_and_knowledge_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Programming</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>technical_skills_and_knowledge_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Data analysis</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>technical_skills_and_knowledge_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>multimedia_design</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Multimedia design</t>
         </is>
       </c>
     </row>
